--- a/artfynd/A 15060-2022 artfynd.xlsx
+++ b/artfynd/A 15060-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15060-2022 artfynd.xlsx
+++ b/artfynd/A 15060-2022 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62123632</v>
+        <v>62123631</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Måsta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585368.8896186787</v>
+        <v>585299</v>
       </c>
       <c r="R2" t="n">
-        <v>6585098.231434931</v>
+        <v>6585120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2016-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62123631</v>
+        <v>95527327</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +787,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måsta, Srm</t>
+          <t>Bäckhagavägen 14, Eskilstuna, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585298.9898424376</v>
+        <v>585248</v>
       </c>
       <c r="R3" t="n">
-        <v>6585120.087920111</v>
+        <v>6585131</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,80 +872,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Joachim Strengbom</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Stadens biologiska mångfald (LONA)</t>
-        </is>
-      </c>
+          <t>Joachim Strengbom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95527327</v>
+        <v>62123632</v>
       </c>
       <c r="B4" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäckhagavägen 14, Eskilstuna, Srm</t>
+          <t>Måsta, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585248.2163886777</v>
+        <v>585369</v>
       </c>
       <c r="R4" t="n">
-        <v>6585131.169080284</v>
+        <v>6585098</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joachim Strengbom</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joachim Strengbom</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Stadens biologiska mångfald (LONA)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15060-2022 artfynd.xlsx
+++ b/artfynd/A 15060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Stadens biologiska mångfald (LONA)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62123631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95527327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
           <t>Stadens biologiska mångfald (LONA)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62123632</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>